--- a/SuppXLS/Scen_UC_RNWHEAT_MANHEAT_20_50.xlsx
+++ b/SuppXLS/Scen_UC_RNWHEAT_MANHEAT_20_50.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEF10E63-F4B6-4A33-A659-C99397EC4CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A47744-B88E-4DAE-A5C4-94755F501DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
     <sheet name="RNWHEAT_MANHEAT_20_50" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>UC - Each Region/Period</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>UC_RNWHEAT_MANHEAT_20_50</t>
+  </si>
+  <si>
+    <t>DMD</t>
   </si>
 </sst>
 </file>
@@ -711,9 +714,12 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8"/>
       <c r="G6" t="s">
         <v>19</v>
       </c>
@@ -744,9 +750,12 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="8"/>
       <c r="G7" t="s">
         <v>19</v>
       </c>
